--- a/codigos/Codigos_resNet/datos/deuda multilaterales.xlsx
+++ b/codigos/Codigos_resNet/datos/deuda multilaterales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\codigos\Codigos_resNet\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C854EA-76F8-4151-AEC0-EEA807F31116}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B34DFCF-C8B8-495A-B78E-9CF71CDDBC28}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{CAA6EF67-7BC3-4A65-9827-9E2B82094EBF}"/>
   </bookViews>
@@ -21,6 +21,9 @@
     <sheet name="bopreal_4" sheetId="6" r:id="rId6"/>
     <sheet name="dep y encajes" sheetId="2" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -93,7 +96,7 @@
     <numFmt numFmtId="179" formatCode="_-* #,##0.00\ [$€]_-;\-* #,##0.00\ [$€]_-;_-* &quot;-&quot;??\ [$€]_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,12 +330,6 @@
     <font>
       <sz val="10"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="28">
@@ -2067,6 +2064,190 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="B.C.R.A."/>
+      <sheetName val="Observaciones"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1146">
+          <cell r="L1146">
+            <v>-41152534525</v>
+          </cell>
+          <cell r="AD1146">
+            <v>761825004.98491001</v>
+          </cell>
+          <cell r="AH1146">
+            <v>24998687967</v>
+          </cell>
+          <cell r="AQ1146">
+            <v>1447.6657</v>
+          </cell>
+        </row>
+        <row r="1147">
+          <cell r="L1147">
+            <v>-39961109838</v>
+          </cell>
+          <cell r="AD1147">
+            <v>750684127.72127998</v>
+          </cell>
+          <cell r="AH1147">
+            <v>23925899640</v>
+          </cell>
+          <cell r="AQ1147">
+            <v>1408.9662000000001</v>
+          </cell>
+        </row>
+        <row r="1148">
+          <cell r="L1148" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1148" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1148" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1148">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1149">
+          <cell r="L1149" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1149" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1149" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1149">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1150">
+          <cell r="L1150" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1150" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1150" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1150">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1151">
+          <cell r="L1151" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1151" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1151" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1151">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1152">
+          <cell r="L1152" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1152" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1152" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1152">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1153">
+          <cell r="L1153" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1153" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1153" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1153">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1154">
+          <cell r="L1154" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1154" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1154" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1154">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1155">
+          <cell r="L1155" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1155" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1155" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1155">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1156">
+          <cell r="L1156" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1156" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1156" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1156">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="1157">
+          <cell r="L1157" t="str">
+            <v/>
+          </cell>
+          <cell r="AD1157" t="str">
+            <v/>
+          </cell>
+          <cell r="AH1157" t="str">
+            <v/>
+          </cell>
+          <cell r="AQ1157">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -3823,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66326B90-32E5-4EC9-AB59-9078B62DF326}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -5760,18 +5941,18 @@
         <v>1194.0833</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E74" si="3">+B67/D67</f>
+        <f t="shared" ref="E67:E85" si="3">+B67/D67</f>
         <v>4679772.6162499962</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F74" si="4">+C67/D67</f>
+        <f t="shared" ref="F67:F85" si="4">+C67/D67</f>
         <v>11505047.33296245</v>
       </c>
       <c r="G67" s="8">
         <v>-26767080944</v>
       </c>
       <c r="H67" s="2">
-        <f t="shared" ref="H67:H74" si="5">+-G67/(D67*1000)</f>
+        <f t="shared" ref="H67:H85" si="5">+-G67/(D67*1000)</f>
         <v>22416.426847272716</v>
       </c>
     </row>
@@ -5954,12 +6135,15 @@
         <v>46023</v>
       </c>
       <c r="B74" s="3">
+        <f>+[1]B.C.R.A.!$AD1146</f>
         <v>761825004.98491001</v>
       </c>
       <c r="C74" s="3">
+        <f>+[1]B.C.R.A.!$AH1146</f>
         <v>24998687967</v>
       </c>
       <c r="D74" s="8">
+        <f>+[1]B.C.R.A.!$AQ1146</f>
         <v>1447.6657</v>
       </c>
       <c r="E74">
@@ -5971,11 +6155,375 @@
         <v>17268273.99930799</v>
       </c>
       <c r="G74" s="8">
+        <f>+[1]B.C.R.A.!$L1146</f>
         <v>-41152534525</v>
       </c>
       <c r="H74" s="2">
+        <f>+-G74/(D74*1000)</f>
+        <v>28426.821554865881</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B75" s="7">
+        <f>+[1]B.C.R.A.!$AD1147</f>
+        <v>750684127.72127998</v>
+      </c>
+      <c r="C75" s="7">
+        <f>+[1]B.C.R.A.!$AH1147</f>
+        <v>23925899640</v>
+      </c>
+      <c r="D75" s="8">
+        <f>+[1]B.C.R.A.!$AQ1147</f>
+        <v>1408.9662000000001</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="3"/>
+        <v>532790.72821000242</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="4"/>
+        <v>16981173.600899722</v>
+      </c>
+      <c r="G75" s="8">
+        <f>+[1]B.C.R.A.!$L1147</f>
+        <v>-39961109838</v>
+      </c>
+      <c r="H75" s="2">
         <f t="shared" si="5"/>
-        <v>28426.821554865881</v>
+        <v>28362.007433535309</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B76" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1148</f>
+        <v/>
+      </c>
+      <c r="C76" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1148</f>
+        <v/>
+      </c>
+      <c r="D76" s="8">
+        <f>+[1]B.C.R.A.!$AQ1148</f>
+        <v>0</v>
+      </c>
+      <c r="E76" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F76" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G76" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1148</f>
+        <v/>
+      </c>
+      <c r="H76" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B77" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1149</f>
+        <v/>
+      </c>
+      <c r="C77" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1149</f>
+        <v/>
+      </c>
+      <c r="D77" s="8">
+        <f>+[1]B.C.R.A.!$AQ1149</f>
+        <v>0</v>
+      </c>
+      <c r="E77" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F77" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G77" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1149</f>
+        <v/>
+      </c>
+      <c r="H77" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B78" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1150</f>
+        <v/>
+      </c>
+      <c r="C78" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1150</f>
+        <v/>
+      </c>
+      <c r="D78" s="8">
+        <f>+[1]B.C.R.A.!$AQ1150</f>
+        <v>0</v>
+      </c>
+      <c r="E78" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F78" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G78" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1150</f>
+        <v/>
+      </c>
+      <c r="H78" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B79" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1151</f>
+        <v/>
+      </c>
+      <c r="C79" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1151</f>
+        <v/>
+      </c>
+      <c r="D79" s="8">
+        <f>+[1]B.C.R.A.!$AQ1151</f>
+        <v>0</v>
+      </c>
+      <c r="E79" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F79" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G79" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1151</f>
+        <v/>
+      </c>
+      <c r="H79" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B80" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1152</f>
+        <v/>
+      </c>
+      <c r="C80" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1152</f>
+        <v/>
+      </c>
+      <c r="D80" s="8">
+        <f>+[1]B.C.R.A.!$AQ1152</f>
+        <v>0</v>
+      </c>
+      <c r="E80" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F80" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G80" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1152</f>
+        <v/>
+      </c>
+      <c r="H80" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B81" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1153</f>
+        <v/>
+      </c>
+      <c r="C81" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1153</f>
+        <v/>
+      </c>
+      <c r="D81" s="8">
+        <f>+[1]B.C.R.A.!$AQ1153</f>
+        <v>0</v>
+      </c>
+      <c r="E81" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F81" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G81" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1153</f>
+        <v/>
+      </c>
+      <c r="H81" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B82" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1154</f>
+        <v/>
+      </c>
+      <c r="C82" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1154</f>
+        <v/>
+      </c>
+      <c r="D82" s="8">
+        <f>+[1]B.C.R.A.!$AQ1154</f>
+        <v>0</v>
+      </c>
+      <c r="E82" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F82" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G82" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1154</f>
+        <v/>
+      </c>
+      <c r="H82" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B83" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1155</f>
+        <v/>
+      </c>
+      <c r="C83" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1155</f>
+        <v/>
+      </c>
+      <c r="D83" s="8">
+        <f>+[1]B.C.R.A.!$AQ1155</f>
+        <v>0</v>
+      </c>
+      <c r="E83" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F83" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G83" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1155</f>
+        <v/>
+      </c>
+      <c r="H83" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1">
+        <v>46327</v>
+      </c>
+      <c r="B84" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1156</f>
+        <v/>
+      </c>
+      <c r="C84" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1156</f>
+        <v/>
+      </c>
+      <c r="D84" s="8">
+        <f>+[1]B.C.R.A.!$AQ1156</f>
+        <v>0</v>
+      </c>
+      <c r="E84" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F84" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G84" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1156</f>
+        <v/>
+      </c>
+      <c r="H84" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1">
+        <v>46357</v>
+      </c>
+      <c r="B85" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AD1157</f>
+        <v/>
+      </c>
+      <c r="C85" s="7" t="str">
+        <f>+[1]B.C.R.A.!$AH1157</f>
+        <v/>
+      </c>
+      <c r="D85" s="8">
+        <f>+[1]B.C.R.A.!$AQ1157</f>
+        <v>0</v>
+      </c>
+      <c r="E85" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F85" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G85" s="8" t="str">
+        <f>+[1]B.C.R.A.!$L1157</f>
+        <v/>
+      </c>
+      <c r="H85" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/codigos/Codigos_resNet/datos/deuda multilaterales.xlsx
+++ b/codigos/Codigos_resNet/datos/deuda multilaterales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\codigos\Codigos_resNet\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B34DFCF-C8B8-495A-B78E-9CF71CDDBC28}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D400A0-6655-4CAF-BF7D-095ABBCD66FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{CAA6EF67-7BC3-4A65-9827-9E2B82094EBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CAA6EF67-7BC3-4A65-9827-9E2B82094EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="deuMult" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +74,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="21">
+  <numFmts count="22">
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
@@ -95,8 +96,9 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0.00\ [$€]_-;\-* #,##0.00\ [$€]_-;_-* &quot;-&quot;??\ [$€]_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
+    <numFmt numFmtId="183" formatCode="_-* #,##0.00\ _$_-;\-* #,##0.00\ _$_-;_-* &quot;-&quot;??\ _$_-;_-@_-"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,6 +332,10 @@
     <font>
       <sz val="10"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="28">
@@ -623,7 +629,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="694">
+  <cellStyleXfs count="696">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1343,6 +1349,8 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="183" fontId="37" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1355,7 +1363,7 @@
     <xf numFmtId="3" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="694">
+  <cellStyles count="696">
     <cellStyle name="20% - Accent1" xfId="4" xr:uid="{DFDBF0D3-4484-4FCA-A994-E23AD0A68789}"/>
     <cellStyle name="20% - Accent2" xfId="5" xr:uid="{BDA045F4-FA20-4C4B-AE88-9B6028909DAC}"/>
     <cellStyle name="20% - Accent3" xfId="6" xr:uid="{F59C922F-E438-46CC-8F3D-D3A51F797E9A}"/>
@@ -1789,6 +1797,7 @@
     <cellStyle name="Millares 30" xfId="616" xr:uid="{1C7E8DE5-2C4F-459E-AFFF-9C5B770DB13A}"/>
     <cellStyle name="Millares 31" xfId="523" xr:uid="{5066AF68-AF36-4771-9331-229B5EE63AF9}"/>
     <cellStyle name="Millares 32" xfId="615" xr:uid="{401DC6F3-D789-4CEB-9CA6-9E17BA34B7B4}"/>
+    <cellStyle name="Millares 33" xfId="695" xr:uid="{5EF916D8-E4C2-466C-B2D1-B3159206AB20}"/>
     <cellStyle name="Millares 4" xfId="374" xr:uid="{F44147E2-BC36-4A31-8EB3-0A7E91028DEC}"/>
     <cellStyle name="Millares 4 2" xfId="395" xr:uid="{C948C39B-3D93-4DDC-9302-DAFE446E9F33}"/>
     <cellStyle name="Millares 4 2 2" xfId="396" xr:uid="{39E20D72-F0A3-478A-B334-53A4CCD65248}"/>
@@ -1864,6 +1873,7 @@
     <cellStyle name="Normal 14 2" xfId="603" xr:uid="{5817A0F9-75FC-4D3B-A3B9-F575F93FABC3}"/>
     <cellStyle name="Normal 15" xfId="609" xr:uid="{2B243177-1FD6-4BEA-8FE9-BCCE1950F431}"/>
     <cellStyle name="Normal 16" xfId="693" xr:uid="{5797D2F4-48C7-44B8-87E5-BCE010DE1228}"/>
+    <cellStyle name="Normal 17" xfId="694" xr:uid="{7AF4D6E0-0280-4C92-B5DE-5D6C70C756A8}"/>
     <cellStyle name="Normal 2" xfId="367" xr:uid="{6357C82D-B62E-4901-96BD-1BC1A87D7E95}"/>
     <cellStyle name="Normal 2 2" xfId="412" xr:uid="{DF8D4D17-FFAC-448A-BB73-00FC5A7504CB}"/>
     <cellStyle name="Normal 2 2 2" xfId="449" xr:uid="{46E544CE-DBC0-4AE1-AD15-12342BBA24EC}"/>
@@ -2101,20 +2111,6 @@
             <v>1408.9662000000001</v>
           </cell>
         </row>
-        <row r="1148">
-          <cell r="L1148" t="str">
-            <v/>
-          </cell>
-          <cell r="AD1148" t="str">
-            <v/>
-          </cell>
-          <cell r="AH1148" t="str">
-            <v/>
-          </cell>
-          <cell r="AQ1148">
-            <v>0</v>
-          </cell>
-        </row>
         <row r="1149">
           <cell r="L1149" t="str">
             <v/>
@@ -2243,6 +2239,33 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Serie_diaria"/>
+      <sheetName val="Observaciones"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="87">
+          <cell r="O87">
+            <v>23019231</v>
+          </cell>
+          <cell r="AG87">
+            <v>615900.29197823</v>
+          </cell>
+          <cell r="AI87">
+            <v>1391.6886999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6200,33 +6223,32 @@
       <c r="A76" s="1">
         <v>46082</v>
       </c>
-      <c r="B76" s="7" t="str">
-        <f>+[1]B.C.R.A.!$AD1148</f>
-        <v/>
-      </c>
-      <c r="C76" s="7" t="str">
-        <f>+[1]B.C.R.A.!$AH1148</f>
-        <v/>
+      <c r="B76" s="7">
+        <f>+[2]Serie_diaria!$AG$87*1000</f>
+        <v>615900291.97823</v>
+      </c>
+      <c r="C76" s="7">
+        <f>+[2]Serie_diaria!$O$87*1000</f>
+        <v>23019231000</v>
       </c>
       <c r="D76" s="8">
-        <f>+[1]B.C.R.A.!$AQ1148</f>
-        <v>0</v>
-      </c>
-      <c r="E76" t="e">
+        <f>+[2]Serie_diaria!$AI$87</f>
+        <v>1391.6886999999999</v>
+      </c>
+      <c r="E76">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F76" t="e">
+        <v>442556.07735999441</v>
+      </c>
+      <c r="F76">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G76" s="8" t="str">
-        <f>+[1]B.C.R.A.!$L1148</f>
-        <v/>
-      </c>
-      <c r="H76" s="2" t="e">
+        <v>16540502.915630486</v>
+      </c>
+      <c r="G76" s="8">
+        <v>-33804965048</v>
+      </c>
+      <c r="H76" s="2">
         <f t="shared" si="5"/>
-        <v>#VALUE!</v>
+        <v>24290.608271806763</v>
       </c>
     </row>
     <row r="77" spans="1:8">
